--- a/resources/digital-products/files/dp-adv-cohort-ltv.xlsx
+++ b/resources/digital-products/files/dp-adv-cohort-ltv.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -525,7 +525,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -571,7 +571,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Average order value (£)</t>
+          <t>Average order value ($)</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
@@ -606,7 +606,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Cost to acquire a customer, CAC (£)</t>
+          <t>Cost to acquire a customer, CAC ($)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Contribution per order (£)</t>
+          <t>Contribution per order ($)</t>
         </is>
       </c>
       <c r="B13" s="10">
@@ -634,16 +634,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Lifetime contribution per customer (£)</t>
+          <t>Lifetime contribution per customer ($)</t>
         </is>
       </c>
       <c r="B14" s="10">
         <f>B13*B8</f>
         <v/>
       </c>
-      <c r="C14" s="4">
-        <f> contribution × lifetime orders</f>
-        <v/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>contribution × lifetime orders</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -665,7 +666,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Book: £44 order at 6.5% → £41.14 contribution; ×1.45 = £59.65 lifetime; CAC £28.80 → recouped in the first order.</t>
+          <t>Book: $44 order at 6.5% → $41.14 contribution; ×1.45 = $59.65 lifetime; CAC $28.80 → recouped in the first order.</t>
         </is>
       </c>
     </row>
@@ -693,5 +694,6 @@
     <mergeCell ref="A20:C20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/resources/digital-products/files/dp-adv-cohort-ltv.xlsx
+++ b/resources/digital-products/files/dp-adv-cohort-ltv.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -613,6 +614,8 @@
         <v>28.8</v>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
@@ -663,6 +666,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -670,6 +674,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="12" t="n"/>
       <c r="B19" s="12" t="n"/>
@@ -682,12 +687,17 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
